--- a/elee201_hw_answers_complete.xlsx
+++ b/elee201_hw_answers_complete.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grovecitycollege-my.sharepoint.com/personal/rumbaughlk_gcc_edu/Documents/Documents/Teaching/Linear Circuits/Homework/HW Checker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{DB5B9418-8ABB-46C3-B5E0-9B2F68BAB96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E57E37A-5390-4503-A6BC-6C2E5A8EA579}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{DB5B9418-8ABB-46C3-B5E0-9B2F68BAB96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7026CEB2-D203-4EA5-851A-3ED4C3C75CD0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
   </bookViews>
   <sheets>
     <sheet name="HW2" sheetId="7" r:id="rId1"/>
     <sheet name="HW3" sheetId="3" r:id="rId2"/>
     <sheet name="HW4" sheetId="4" r:id="rId3"/>
-    <sheet name="HW5" sheetId="1" r:id="rId4"/>
-    <sheet name="HW6" sheetId="2" r:id="rId5"/>
+    <sheet name="HW5" sheetId="2" r:id="rId4"/>
+    <sheet name="HW6" sheetId="1" r:id="rId5"/>
     <sheet name="HW7" sheetId="5" r:id="rId6"/>
     <sheet name="HW8" sheetId="6" r:id="rId7"/>
     <sheet name="HW9" sheetId="8" r:id="rId8"/>
@@ -6442,6 +6442,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="4" max="4" width="17.08984375" customWidth="1"/>
     <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.54296875" customWidth="1"/>
@@ -8525,6 +8526,247 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D3BB39-110F-4C3C-ACE5-9DDB4799F102}">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="10"/>
+      <c r="B1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="85"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="18">
+        <v>2.29</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="18">
+        <v>2.36</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1">
+        <v>5</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1">
+        <v>125</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="6">
+        <v>1</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.97</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="8">
+        <v>3.99</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7749778-6856-40A2-9432-9BE41E2A7C62}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8727,247 +8969,6 @@
     <mergeCell ref="J1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D3BB39-110F-4C3C-ACE5-9DDB4799F102}">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="10"/>
-      <c r="B1" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="86" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="85"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="18">
-        <v>2.29</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="18">
-        <v>2.36</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1">
-        <v>5</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="1">
-        <v>125</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="6">
-        <v>1</v>
-      </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1.97</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1">
-        <v>10</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="8">
-        <v>3.99</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/elee201_hw_answers_complete.xlsx
+++ b/elee201_hw_answers_complete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grovecitycollege-my.sharepoint.com/personal/rumbaughlk_gcc_edu/Documents/Documents/Teaching/Linear Circuits/Homework/HW Checker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{DB5B9418-8ABB-46C3-B5E0-9B2F68BAB96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7026CEB2-D203-4EA5-851A-3ED4C3C75CD0}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{DB5B9418-8ABB-46C3-B5E0-9B2F68BAB96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55E4F2BE-EA6F-4E18-8ACF-3F521E2F2852}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
   </bookViews>
   <sheets>
     <sheet name="HW2" sheetId="7" r:id="rId1"/>
@@ -8846,7 +8846,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -8858,7 +8858,7 @@
         <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>-120</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
